--- a/dataset/Ввод жилых домов/input.xlsx
+++ b/dataset/Ввод жилых домов/input.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="21"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Содержание" sheetId="1" state="visible" r:id="rId3"/>
@@ -2548,7 +2548,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="Picture 2" descr="">
+        <xdr:cNvPr id="1" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -2593,7 +2593,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 2" descr="">
+        <xdr:cNvPr id="10" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -2638,7 +2638,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 2" descr="">
+        <xdr:cNvPr id="11" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -2683,7 +2683,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 2" descr="">
+        <xdr:cNvPr id="12" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -2728,7 +2728,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 2" descr="">
+        <xdr:cNvPr id="13" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -2773,7 +2773,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 2" descr="">
+        <xdr:cNvPr id="14" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -2818,7 +2818,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 2" descr="">
+        <xdr:cNvPr id="15" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -2863,7 +2863,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Picture 2" descr="">
+        <xdr:cNvPr id="16" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -2908,7 +2908,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Picture 2" descr="">
+        <xdr:cNvPr id="17" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -2953,7 +2953,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Picture 2" descr="">
+        <xdr:cNvPr id="18" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -2998,7 +2998,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Picture 2" descr="">
+        <xdr:cNvPr id="19" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -3043,7 +3043,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 2" descr="">
+        <xdr:cNvPr id="2" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -3088,7 +3088,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Picture 2" descr="">
+        <xdr:cNvPr id="20" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -3133,7 +3133,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="Picture 2" descr="">
+        <xdr:cNvPr id="21" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -3178,7 +3178,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2" descr="">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -3223,7 +3223,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="">
+        <xdr:cNvPr id="4" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -3268,7 +3268,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 2" descr="">
+        <xdr:cNvPr id="5" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -3313,7 +3313,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 2" descr="">
+        <xdr:cNvPr id="6" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -3358,7 +3358,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 2" descr="">
+        <xdr:cNvPr id="7" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -3403,7 +3403,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 2" descr="">
+        <xdr:cNvPr id="8" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -3448,7 +3448,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 2" descr="">
+        <xdr:cNvPr id="9" name="Picture 2">
           <a:hlinkClick r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvPicPr/>
@@ -3611,7 +3611,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:IW30"/>
-  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="4.66"/>
@@ -11298,7 +11298,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W105"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
@@ -14459,7 +14459,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W105"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
@@ -17713,7 +17713,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:R105"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
@@ -20676,7 +20676,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:R105"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
@@ -23727,7 +23727,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K106"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.32"/>
@@ -25498,7 +25498,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J106"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
@@ -28464,7 +28464,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O105"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
@@ -31422,7 +31422,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O105"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
@@ -34380,7 +34380,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q105"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
@@ -37340,7 +37340,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q105"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
@@ -40301,7 +40301,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W105"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.32"/>
@@ -42073,7 +42073,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q105"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
@@ -45033,7 +45033,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q105"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
@@ -47993,7 +47993,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q105"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
@@ -50953,7 +50953,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:T105"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
@@ -53921,7 +53921,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P105"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
@@ -57109,7 +57109,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:S105"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
@@ -60501,7 +60501,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W105"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
@@ -63567,7 +63567,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W105"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
@@ -66633,7 +66633,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W105"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
@@ -69743,7 +69743,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:U105"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
